--- a/payhug-spec/_pipeline/investor_admin/_fig/assets/xlsx/투자수익현황_2026-06-08_2026-08-27.xlsx
+++ b/payhug-spec/_pipeline/investor_admin/_fig/assets/xlsx/투자수익현황_2026-06-08_2026-08-27.xlsx
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>803338</v>
+        <v>2328080</v>
       </c>
     </row>
     <row r="7">
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>0.0457</v>
+        <v>0.1325</v>
       </c>
     </row>
     <row r="8">
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>0.0365</v>
+        <v>0.1058</v>
       </c>
     </row>
   </sheetData>
